--- a/network/file/考勤表25-4.xlsx
+++ b/network/file/考勤表25-4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\network\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10B7E68-A49B-4C86-8775-391AC2025336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E517D1DD-07E6-4D0A-B03D-29F7AE6F4F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -441,9 +441,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -452,6 +449,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -767,6 +767,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:V55"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25"/>
   <cols>
@@ -779,65 +782,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="22.7" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
     </row>
     <row r="2" spans="1:22" ht="14.25" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
     </row>
     <row r="3" spans="1:22" ht="11.25" customHeight="1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -894,14 +897,14 @@
       <c r="U3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="V3" s="8" t="s">
+      <c r="V3" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="11.25" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="2" t="s">
         <v>100</v>
       </c>
@@ -956,7 +959,7 @@
       <c r="U4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="V4" s="8"/>
+      <c r="V4" s="7"/>
     </row>
     <row r="5" spans="1:22" ht="15" customHeight="1">
       <c r="A5" s="3">
@@ -1859,75 +1862,75 @@
       <c r="V34" s="1"/>
     </row>
     <row r="35" spans="1:22" ht="28.5" customHeight="1">
-      <c r="Q35" s="5" t="s">
+      <c r="Q35" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="R35" s="5"/>
-      <c r="S35" s="5"/>
-      <c r="T35" s="5"/>
-      <c r="U35" s="5"/>
-      <c r="V35" s="5"/>
+      <c r="R35" s="8"/>
+      <c r="S35" s="8"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="8"/>
+      <c r="V35" s="8"/>
     </row>
     <row r="36" spans="1:22" ht="22.7" customHeight="1">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
     </row>
     <row r="37" spans="1:22" ht="14.25" customHeight="1">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="7"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="7"/>
-      <c r="V37" s="7"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
+      <c r="U37" s="6"/>
+      <c r="V37" s="6"/>
     </row>
     <row r="38" spans="1:22" ht="11.25" customHeight="1">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>4</v>
       </c>
       <c r="D38" s="2" t="s">
@@ -1984,14 +1987,14 @@
       <c r="U38" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="V38" s="8" t="s">
+      <c r="V38" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="11.25" customHeight="1">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
       <c r="D39" s="2" t="s">
         <v>100</v>
       </c>
@@ -2046,7 +2049,7 @@
       <c r="U39" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="V39" s="8"/>
+      <c r="V39" s="7"/>
     </row>
     <row r="40" spans="1:22" ht="15" customHeight="1">
       <c r="A40" s="3">
@@ -2499,23 +2502,17 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="28.5" customHeight="1">
-      <c r="Q55" s="5" t="s">
+      <c r="Q55" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="R55" s="5"/>
-      <c r="S55" s="5"/>
-      <c r="T55" s="5"/>
-      <c r="U55" s="5"/>
-      <c r="V55" s="5"/>
+      <c r="R55" s="8"/>
+      <c r="S55" s="8"/>
+      <c r="T55" s="8"/>
+      <c r="U55" s="8"/>
+      <c r="V55" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="V3:V4"/>
     <mergeCell ref="Q55:V55"/>
     <mergeCell ref="Q35:V35"/>
     <mergeCell ref="A36:V36"/>
@@ -2524,6 +2521,12 @@
     <mergeCell ref="B38:B39"/>
     <mergeCell ref="C38:C39"/>
     <mergeCell ref="V38:V39"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="V3:V4"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
@@ -2533,7 +2536,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="7.874015748031496E-2" right="7.874015748031496E-2" top="0.27559055118110237" bottom="0.39370078740157483" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="35" max="16383" man="1"/>
   </rowBreaks>
